--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487501_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487501_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9117</v>
+        <v>4.5275</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1803</v>
+        <v>2.6782</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7314</v>
+        <v>1.8493</v>
       </c>
       <c r="G2" t="n">
         <v>1.3425</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7271</v>
+        <v>1.3429</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7479</v>
+        <v>0.2458</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9791</v>
+        <v>1.097</v>
       </c>
       <c r="V2" t="n">
         <v>0.2754</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>M. JUAN SEVILLANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5779</v>
+        <v>4.3737</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6135</v>
+        <v>2.3433</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9645</v>
+        <v>2.0304</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7216</v>
+        <v>-0.3575</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5703</v>
+        <v>1.4063</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8487</v>
+        <v>-1.7638</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0373</v>
+        <v>1.0353</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6339</v>
+        <v>2.4209</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5966</v>
+        <v>-1.3856</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3157</v>
+        <v>-1.3927</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0635</v>
+        <v>-1.0145</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2521</v>
+        <v>-0.3782</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7626</v>
+        <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1305</v>
+        <v>0.5353</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.387</v>
+        <v>-0.1459</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5175</v>
+        <v>0.6812</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0576</v>
+        <v>2.4332</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0576</v>
+        <v>2.4332</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. JUAN SEVILLANO</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1257</v>
+        <v>3.9981</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3894</v>
+        <v>1.9534</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7364</v>
+        <v>2.0447</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3575</v>
+        <v>2.7216</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4063</v>
+        <v>3.5703</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7638</v>
+        <v>-0.8487</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0353</v>
+        <v>3.0373</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4209</v>
+        <v>3.6339</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3856</v>
+        <v>-0.5966</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3927</v>
+        <v>-0.3157</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0145</v>
+        <v>-0.0635</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3782</v>
+        <v>-0.2521</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7126</v>
+        <v>0.5506</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0998</v>
+        <v>-0.0471</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3872</v>
+        <v>0.5977</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4332</v>
+        <v>-0.0576</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4332</v>
+        <v>-0.0576</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0042</v>
+        <v>3.1718</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9737</v>
+        <v>2.1948</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0305</v>
+        <v>0.977</v>
       </c>
       <c r="G5" t="n">
         <v>2.0201</v>
@@ -844,13 +844,13 @@
         <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6707</v>
+        <v>0.8384</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0288</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6419</v>
+        <v>0.5884</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6659</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8151</v>
+        <v>0.2562</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5838</v>
+        <v>1.1051</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7687</v>
+        <v>-0.8489</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5546</v>
@@ -922,13 +922,13 @@
         <v>2.9377</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7027</v>
+        <v>1.1438</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6499</v>
+        <v>0.1711</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0528</v>
+        <v>0.9726</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3329</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0414</v>
+        <v>0.1438</v>
       </c>
       <c r="E7" t="n">
-        <v>0.065</v>
+        <v>0.1674</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0236</v>
@@ -1000,10 +1000,10 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4511</v>
+        <v>0.5534</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2664</v>
+        <v>0.3688</v>
       </c>
       <c r="U7" t="n">
         <v>0.1847</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3185</v>
+        <v>-0.8778</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4596</v>
+        <v>-1.1526</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1411</v>
+        <v>0.2748</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4835</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4214</v>
+        <v>0.0193</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2376</v>
+        <v>0.0694</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1838</v>
+        <v>-0.0501</v>
       </c>
       <c r="V8" t="n">
         <v>0.3905</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.34</v>
+        <v>-1.9853</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4708</v>
+        <v>-1.4904</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8692</v>
+        <v>-0.495</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0345</v>
@@ -1156,13 +1156,13 @@
         <v>1.9585</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8343</v>
+        <v>-0.4796</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4256</v>
+        <v>-0.4452</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4086</v>
+        <v>-0.0344</v>
       </c>
       <c r="V9" t="n">
         <v>1.5495</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4602</v>
+        <v>-3.5671</v>
       </c>
       <c r="E10" t="n">
         <v>-1.9975</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4627</v>
+        <v>-1.5697</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1785</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1066</v>
+        <v>-0.2135</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0472</v>
+        <v>-0.1541</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7643</v>
+        <v>-4.2597</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9778</v>
+        <v>-4.7137</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2134</v>
+        <v>0.454</v>
       </c>
       <c r="G11" t="n">
         <v>-5.4084</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.493</v>
+        <v>0.0116</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3276</v>
+        <v>-0.0635</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1654</v>
+        <v>0.0751</v>
       </c>
       <c r="V11" t="n">
         <v>0.9412</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.592999999999998</v>
+        <v>5.781200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.09999999999999964</v>
+        <v>1.087999999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>4.693099999999999</v>
+        <v>4.693000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.754900000000001</v>
+        <v>-5.7549</v>
       </c>
       <c r="H12" t="n">
         <v>3.7445</v>
@@ -1381,7 +1381,7 @@
         <v>-5.906499999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>3.916800000000001</v>
+        <v>3.9168</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.7714</v>
@@ -1390,13 +1390,13 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1142</v>
+        <v>4.302199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8440000000000001</v>
+        <v>0.344</v>
       </c>
       <c r="U12" t="n">
-        <v>3.9582</v>
+        <v>3.9581</v>
       </c>
       <c r="V12" t="n">
         <v>3.316800000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9933</v>
+        <v>2.6037</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3067</v>
+        <v>2.1888</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6866</v>
+        <v>0.4149</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4536</v>
+        <v>3.6179</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3838</v>
+        <v>0.7629</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9303</v>
+        <v>2.855</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1809</v>
+        <v>2.3711</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0308</v>
+        <v>0.3504</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2117</v>
+        <v>2.0208</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6345</v>
+        <v>1.2467</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.353</v>
+        <v>0.4125</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7186</v>
+        <v>0.8343</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1543</v>
+        <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0125</v>
+        <v>0.1276</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8457</v>
+        <v>0.0135</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1668</v>
+        <v>0.1141</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4344</v>
+        <v>-2.7086</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4344</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>M. TRAORE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1852</v>
+        <v>1.1527</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9842</v>
+        <v>4.0616</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2011</v>
+        <v>-2.9089</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6179</v>
+        <v>2.1992</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7629</v>
+        <v>0.2889</v>
       </c>
       <c r="I14" t="n">
-        <v>2.855</v>
+        <v>1.9103</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3711</v>
+        <v>4.0044</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3504</v>
+        <v>2.6658</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0208</v>
+        <v>1.3385</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2467</v>
+        <v>-1.8052</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4125</v>
+        <v>-2.3769</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8343</v>
+        <v>0.5717</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5668</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1958</v>
+        <v>-2.1543</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7626</v>
+        <v>0.9792</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2909</v>
+        <v>-0.8127</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1911</v>
+        <v>-0.497</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0997</v>
+        <v>-0.3157</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.7086</v>
+        <v>0.9412</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7086</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. RUBIN CARBALLEIRA</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6218</v>
+        <v>1.1237</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.019</v>
+        <v>-0.9214</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6408</v>
+        <v>2.0451</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7227</v>
+        <v>-0.4536</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4093</v>
+        <v>-1.3838</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3133</v>
+        <v>0.9303</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0404</v>
+        <v>0.1809</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.0308</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>0.2117</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6822</v>
+        <v>-0.6345</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4093</v>
+        <v>-1.353</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2729</v>
+        <v>0.7186</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2967</v>
+        <v>0.1429</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0594</v>
+        <v>-0.3823</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2373</v>
+        <v>0.5252</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4344</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4344</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TRAORE</t>
+          <t>X. RUBIN CARBALLEIRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5654</v>
+        <v>0.6753</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4476</v>
+        <v>-0.019</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8822</v>
+        <v>0.6943</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1992</v>
+        <v>0.7227</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2889</v>
+        <v>0.4093</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9103</v>
+        <v>0.3133</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0044</v>
+        <v>0.0404</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6658</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3385</v>
+        <v>0.0404</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8052</v>
+        <v>0.6822</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3769</v>
+        <v>0.4093</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5717</v>
+        <v>0.2729</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3999</v>
+        <v>-0.2432</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.111</v>
+        <v>-0.0594</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2889</v>
+        <v>-0.1838</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4006</v>
+        <v>-0.2448</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0171</v>
+        <v>0.0852</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3834</v>
+        <v>-0.33</v>
       </c>
       <c r="G17" t="n">
         <v>0.1714</v>
@@ -1780,13 +1780,13 @@
         <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4925</v>
+        <v>-0.3367</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3737</v>
+        <v>-0.3202</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7134</v>
+        <v>-0.6867</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1188</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5946</v>
+        <v>-0.5679</v>
       </c>
       <c r="G18" t="n">
         <v>-0.476</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2374</v>
+        <v>-0.2107</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3061</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9494</v>
+        <v>-2.7447</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6433</v>
+        <v>1.8037</v>
       </c>
       <c r="G19" t="n">
         <v>0.759</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0858</v>
+        <v>-0.7208</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1416</v>
+        <v>-0.9369</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0558</v>
+        <v>0.2162</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6274</v>
+        <v>-1.8634</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3144</v>
+        <v>-2.4168</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.5533</v>
       </c>
       <c r="G20" t="n">
         <v>1.4555</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.1645</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.904</v>
+        <v>-1.0063</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9754</v>
+        <v>0.8418</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9114</v>
+        <v>-6.4127</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0127</v>
+        <v>-4.808</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8987</v>
+        <v>-1.6046</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2411</v>
@@ -2092,13 +2092,13 @@
         <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3949</v>
+        <v>-0.8962</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1592</v>
+        <v>-0.9546</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2357</v>
+        <v>0.0584</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1003</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.593200000000001</v>
+        <v>-4.5932</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6929</v>
+        <v>-4.693099999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09989999999999988</v>
+        <v>0.09990000000000032</v>
       </c>
       <c r="G22" t="n">
         <v>5.755000000000001</v>
@@ -2140,7 +2140,7 @@
         <v>-3.7445</v>
       </c>
       <c r="I22" t="n">
-        <v>9.499400000000001</v>
+        <v>9.4994</v>
       </c>
       <c r="J22" t="n">
         <v>8.927300000000001</v>
@@ -2149,7 +2149,7 @@
         <v>3.0206</v>
       </c>
       <c r="L22" t="n">
-        <v>5.906499999999999</v>
+        <v>5.9065</v>
       </c>
       <c r="M22" t="n">
         <v>-3.1724</v>
@@ -2170,13 +2170,13 @@
         <v>10.7714</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.1141</v>
+        <v>-3.1143</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.9582</v>
+        <v>-3.9583</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8441000000000003</v>
+        <v>0.8441000000000002</v>
       </c>
       <c r="V22" t="n">
         <v>-3.317</v>
